--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556346.4474981561</v>
+        <v>556346</v>
       </c>
       <c r="R2" t="n">
-        <v>6395007.402520278</v>
+        <v>6395007</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1978-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556346.4474981561</v>
+        <v>556346</v>
       </c>
       <c r="R3" t="n">
-        <v>6395007.402520278</v>
+        <v>6395007</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +850,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99601</v>
+        <v>99606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99606</v>
+        <v>99607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99607</v>
+        <v>99634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99640</v>
+        <v>99647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99647</v>
+        <v>99651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99651</v>
+        <v>99658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99661</v>
+        <v>99666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99666</v>
+        <v>99674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153207</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>74314369</v>
       </c>
       <c r="B3" t="n">
-        <v>99674</v>
+        <v>99684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74153207</v>
+        <v>74314369</v>
       </c>
       <c r="B2" t="n">
-        <v>98589</v>
+        <v>100142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>222467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L28 Norrbyn 700 m SV, Sm</t>
+          <t>Alsta by 800 m S, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -736,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1985-12-31</t>
+          <t>1983-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G9b 1533. SOM: Dactylorhiza maculata ssp. maculata. LEG: Birger Danielsson</t>
+          <t>Smålands flora 2007: KOO: 6G9b 1533. SOM: Eriophorum latifolium. LEG: Birger Danielsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74314369</v>
+        <v>74153207</v>
       </c>
       <c r="B3" t="n">
-        <v>99684</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222467</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alsta by 800 m S, Sm</t>
+          <t>L28 Norrbyn 700 m SV, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -847,17 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1978-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1983-12-31</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G9b 1533. SOM: Eriophorum latifolium. LEG: Birger Danielsson</t>
+          <t>Smålands flora 2007: KOO: 6G9b 1533. SOM: Dactylorhiza maculata ssp. maculata. LEG: Birger Danielsson</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17935-2025 artfynd.xlsx
+++ b/artfynd/A 17935-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74314369</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>